--- a/iq_adoption_equipfoods_tsm.xlsx
+++ b/iq_adoption_equipfoods_tsm.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,9 +35,9 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="004A3AB5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -53,6 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -99,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +116,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -117,6 +126,7 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,14 +492,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>iQ adoption by user — all-time. Excludes Equipfoods Pulse (analytics.saras@equipfoods.com).</t>
+          <t>Time period: ALL TIME (all available data — dashboard range May 3, 2026 – Sep 11, 2026)</t>
         </is>
       </c>
     </row>
@@ -517,17 +528,22 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>iQ Native</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>iQ MCP</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Total Questions</t>
         </is>
@@ -544,13 +560,18 @@
           <t>suraj@equipfoods.com</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -565,13 +586,18 @@
           <t>deanna@equipfoods.com</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -586,178 +612,247 @@
           <t>alexb@equipfoods.com</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>3 users</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>None of these users were active in the last 30 / 14 / 7 days — recent EquipFoods volume is all Equipfoods Pulse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>These are all-time figures. None of these three users were active in the last 30 days, last 14 days, or last 7 days — their activity sits entirely outside those windows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Excludes the Equipfoods Pulse account (analytics.saras@equipfoods.com), which is the only EquipFoods account with activity in the last 30 / 14 / 7 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>TrueSeaMoss (TSM)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>iQ adoption by user — all-time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Time period: ALL TIME (all available data — dashboard range May 3, 2026 – Sep 11, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>iQ Native</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>iQ MCP</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Total Questions</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TrueSeaMossProd Iq</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Analytics Saras</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>gega trueseamoss</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>11</v>
+          <t>TrueSeaMossProd Iq</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>email not shown in dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>p.josanu</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="6" t="n">
+          <t>Analytics Saras</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>analyticssaras@trueseamoss.com</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>gega trueseamoss</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>gega@trueseamoss.com</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>p josanu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>p.josanu@trueseamoss.com</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>4 users</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C22" s="8" t="inlineStr"/>
+      <c r="D22" s="9" t="n">
         <v>102</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="E22" s="9" t="n">
         <v>113</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="F22" s="9" t="n">
         <v>215</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Last 7 days: Analytics Saras only (3 questions, all iQ MCP). TrueSeaMossProd Iq, gega and p.josanu are inactive in that window.</t>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>These are all-time figures. Recent windows are much smaller: last 30 days = 13 questions / 3 users, last 14 days = 7 questions / 2 users, last 7 days = 3 questions / 1 user (Analytics Saras, all via iQ MCP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>gega trueseamoss and TrueSeaMossProd Iq were active in the 14- and 30-day windows but not in the last 7 days; p josanu is all-time only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>The dashboard's external-customers-only view lists 3 TSM users (106 questions) and does not show TrueSeaMossProd Iq or its email; that account's 109 questions are included above to reach the 215 all-time total.</t>
         </is>
       </c>
     </row>

--- a/iq_adoption_equipfoods_tsm.xlsx
+++ b/iq_adoption_equipfoods_tsm.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -712,38 +712,38 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TrueSeaMossProd Iq</t>
+          <t>gega trueseamoss</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>email not shown in dashboard</t>
+          <t>gega@trueseamoss.com</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>109</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Analytics Saras</t>
+          <t>p josanu</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>analyticssaras@trueseamoss.com</t>
+          <t>p.josanu@trueseamoss.com</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -752,107 +752,55 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>gega trueseamoss</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>gega@trueseamoss.com</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>p josanu</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>p.josanu@trueseamoss.com</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Multi</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>2 users</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>2</v>
+      <c r="F20" s="9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>4 users</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr"/>
-      <c r="D22" s="9" t="n">
-        <v>102</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>113</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>215</v>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>These are all-time figures. Excludes Analytics Saras (analyticssaras@trueseamoss.com) and TrueSeaMossProd Iq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>gega trueseamoss was active in the last 30 and 14 days (3 questions, iQ Native) but not in the last 7 days. p josanu shows all-time activity only.</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>These are all-time figures. Recent windows are much smaller: last 30 days = 13 questions / 3 users, last 14 days = 7 questions / 2 users, last 7 days = 3 questions / 1 user (Analytics Saras, all via iQ MCP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>gega trueseamoss and TrueSeaMossProd Iq were active in the 14- and 30-day windows but not in the last 7 days; p josanu is all-time only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>The dashboard's external-customers-only view lists 3 TSM users (106 questions) and does not show TrueSeaMossProd Iq or its email; that account's 109 questions are included above to reach the 215 all-time total.</t>
+          <t>Neither of these two users was active in the last 7 days.</t>
         </is>
       </c>
     </row>

--- a/iq_adoption_equipfoods_tsm.xlsx
+++ b/iq_adoption_equipfoods_tsm.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,7 +31,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="002D2D2D"/>
-      <sz val="13"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002D2D2D"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -105,28 +111,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -510,297 +520,527 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>All Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Time period: ALL TIME (all available data — dashboard range May 3, 2026 – Sep 11, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>iQ Native</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>iQ MCP</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Total Questions</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Suraj Dave</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>suraj@equipfoods.com</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Native</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Deanna Eng</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>deanna@equipfoods.com</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Native</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Alex Beshansky</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>alexb@equipfoods.com</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Native</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>3 users</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F10" s="11" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>These are all-time figures. None of these three users were active in the last 30 days, last 14 days, or last 7 days — their activity sits entirely outside those windows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>These are all-time figures. None of these three users were active in the last 30 days, last 14 days, or last 7 days — their activity sits entirely outside those windows, so there is no separate 30-day or 14-day section for EquipFoods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Excludes the Equipfoods Pulse account (analytics.saras@equipfoods.com), which is the only EquipFoods account with activity in the last 30 / 14 / 7 days.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>TrueSeaMoss (TSM)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>All sections below exclude Analytics Saras (analyticssaras@trueseamoss.com) and TrueSeaMossProd Iq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>All Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Time period: ALL TIME (all available data — dashboard range May 3, 2026 – Sep 11, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>iQ Native</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>iQ MCP</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Total Questions</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>gega trueseamoss</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>gega@trueseamoss.com</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Native</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D23" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E23" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>p josanu</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>p.josanu@trueseamoss.com</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D24" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E24" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>2 users</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr"/>
-      <c r="D20" s="9" t="n">
+      <c r="C25" s="10" t="inlineStr"/>
+      <c r="D25" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E25" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F25" s="11" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>These are all-time figures. Excludes Analytics Saras (analyticssaras@trueseamoss.com) and TrueSeaMossProd Iq.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>gega trueseamoss was active in the last 30 and 14 days (3 questions, iQ Native) but not in the last 7 days. p josanu shows all-time activity only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Neither of these two users was active in the last 7 days.</t>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Full TSM all-time volume is 215 questions / 4 users; the two excluded accounts account for 202 of those questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Last 30 Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Time period: LAST 30 DAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>iQ Native</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>iQ MCP</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Total Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>gega trueseamoss</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>gega@trueseamoss.com</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>1 user</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr"/>
+      <c r="D34" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>p josanu had no activity in this window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Full TSM last-30-day volume is 13 questions / 3 users — the other 10 questions belong to the two excluded accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Last 14 Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Time period: LAST 14 DAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>iQ Native</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>iQ MCP</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Total Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>gega trueseamoss</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>gega@trueseamoss.com</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>1 user</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr"/>
+      <c r="D44" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Identical to the last-30-day figures — all of gega's recent activity falls inside the last 14 days. p josanu had no activity in this window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Full TSM last-14-day volume is 7 questions / 2 users — the other 4 belong to Analytics Saras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Last 7 days is not shown because it would be empty: the only TSM user active in that window was Analytics Saras (3 questions, iQ MCP), which is excluded here.</t>
         </is>
       </c>
     </row>
